--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,187 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5206000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4822000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4817000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4707000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4938000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4576000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4484000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4343000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4589000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8692000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3050000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2887000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2877000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2816000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3006000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2803000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2688000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2665000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2727000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5146000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2156000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1935000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1940000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1891000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1932000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1773000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1796000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1678000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1862000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3546000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,46 +863,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E12" s="3">
         <v>322000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>298000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>270000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>271000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>260000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>257000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>238000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>225000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>391000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +984,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1025,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4517000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4205000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4247000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4148000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4161000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3971000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3853000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3834000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3862000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7276000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>689000</v>
+      </c>
+      <c r="E18" s="3">
         <v>617000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>570000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>559000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>777000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>605000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>631000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>509000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>727000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1416000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,198 +1140,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E20" s="3">
         <v>157000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>137000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>123000</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>19000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>20000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>28000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>34000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>52000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E21" s="3">
         <v>927000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>863000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>839000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>934000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>784000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>808000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>696000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>915000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1784000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E22" s="3">
         <v>138000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>137000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>136000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>59000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>609000</v>
+      </c>
+      <c r="E23" s="3">
         <v>636000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>570000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>546000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>718000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>622000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>639000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>533000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>755000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1444000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E24" s="3">
         <v>250000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>137000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>163000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>151000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>128000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>153000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>131000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>179000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>261000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>416000</v>
+      </c>
+      <c r="E26" s="3">
         <v>386000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>433000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>383000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>567000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>494000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>486000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>402000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>576000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1183000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E27" s="3">
         <v>379000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>418000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>189000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>548000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>488000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>473000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>389000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>564000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1162000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,46 +1507,52 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-4000</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3">
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3">
         <v>6000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>12000</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>7000</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-157000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-137000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-123000</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-19000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-20000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-28000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-34000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-52000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E33" s="3">
         <v>375000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>418000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>189000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>554000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>488000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>485000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>389000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>564000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1169000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E35" s="3">
         <v>375000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>418000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>189000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>554000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>488000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>485000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>389000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>564000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1169000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,32 +1876,33 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2504000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2418000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1939000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2327000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1445000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>500000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>525000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1829,8 +1915,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,32 +1956,35 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4557000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4438000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4441000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4387000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4301000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3990000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4141000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1905,32 +1997,35 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1960000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2128000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2264000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2256000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2155000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2237000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,32 +2038,35 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E45" s="3">
         <v>484000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>596000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>634000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>417000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>588000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>505000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,32 +2079,35 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9410000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9468000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9240000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9604000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8318000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7278000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7408000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,8 +2120,11 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2057,32 +2161,35 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2355000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2357000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2327000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2314000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2080000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2161000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,32 +2202,35 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14189000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14246000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14352000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14418000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14333000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14365000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14520000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2133,8 +2243,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,32 +2325,35 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6355000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6313000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6362000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6288000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2574000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2344000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2375000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2247,8 +2366,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,32 +2407,35 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32454000</v>
+      </c>
+      <c r="E54" s="3">
         <v>32382000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32311000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32637000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27539000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26067000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26464000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2323,8 +2448,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,32 +2484,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2947000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2774000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2835000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2977000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2944000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2687000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2702000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,32 +2523,35 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1006000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5000</v>
       </c>
       <c r="F58" s="3">
         <v>5000</v>
       </c>
       <c r="G58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H58" s="3">
         <v>15000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2431,32 +2564,35 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5028000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4784000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4741000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5254000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4232000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3936000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3985000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,32 +2605,35 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8981000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7565000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7581000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8236000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7191000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6635000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6693000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2507,32 +2646,35 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8436000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10253000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10233000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10234000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8234000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2545,32 +2687,35 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7727000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7261000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7174000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7270000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2522000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2325000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2467000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2583,8 +2728,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,32 +2851,35 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25321000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25251000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25209000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25947000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18182000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9208000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9433000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +2892,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,32 +3073,35 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1326000</v>
+      </c>
+      <c r="E72" s="3">
         <v>937000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>576000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>185000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11235000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18801000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18680000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2941,8 +3114,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,32 +3237,35 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7133000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7131000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7102000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6690000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9357000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16859000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17031000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3278,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E81" s="3">
         <v>375000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>418000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>189000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>554000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>488000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>485000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>389000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>564000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1169000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E83" s="3">
         <v>153000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>156000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>157000</v>
       </c>
       <c r="G83" s="3">
         <v>157000</v>
       </c>
       <c r="H83" s="3">
+        <v>157000</v>
+      </c>
+      <c r="I83" s="3">
         <v>160000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>157000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>159000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>154000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>316000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1050000</v>
+      </c>
+      <c r="E89" s="3">
         <v>650000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-67000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>468000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1042000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>622000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>468000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1040000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-80000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-70000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-143000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-74000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-73000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-120000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-84000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-266000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-95000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-118000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-85000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-145000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,17 +3910,18 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-14000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -3716,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4072,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-900000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-227000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>673000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-37000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-505000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>140000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-420000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1401000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-31000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-25000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-11000</v>
       </c>
       <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>-11000</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E102" s="3">
         <v>475000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-389000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>883000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>947000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>24000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-55000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-153000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-195000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>GEHC</t>
   </si>
@@ -656,199 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4650000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5206000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4822000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4817000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4707000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4938000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4576000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4484000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4343000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4589000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8692000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2749000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3050000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2887000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2877000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2816000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3006000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2803000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2688000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2665000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2727000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5146000</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1901000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2156000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1935000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1940000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1891000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1932000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1773000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1796000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1678000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1862000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3546000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,49 +877,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E12" s="3">
         <v>315000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>322000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>298000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>270000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>271000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>260000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>257000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>238000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>225000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>391000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4110000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4517000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4205000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4247000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4148000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4161000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3971000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3853000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3834000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3862000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7276000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E18" s="3">
         <v>689000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>617000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>570000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>559000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>777000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>605000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>631000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>509000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>727000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1416000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,213 +1174,229 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E20" s="3">
         <v>51000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>157000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>137000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>123000</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>19000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>20000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>28000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>52000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>782000</v>
+      </c>
+      <c r="E21" s="3">
         <v>884000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>927000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>863000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>839000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>934000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>784000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>808000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>696000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>915000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1784000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E22" s="3">
         <v>131000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>138000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>137000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>136000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>59000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24000</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E23" s="3">
         <v>609000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>636000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>570000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>546000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>718000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>622000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>639000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>533000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>755000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1444000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E24" s="3">
         <v>193000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>250000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>137000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>163000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>151000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>128000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>153000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>131000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>179000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>261000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E26" s="3">
         <v>416000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>386000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>433000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>383000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>567000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>494000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>486000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>402000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>576000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1183000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E27" s="3">
         <v>403000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>379000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>418000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>189000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>548000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>488000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>473000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>389000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>564000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1162000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,49 +1568,55 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-4000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3">
         <v>6000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>12000</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>7000</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-51000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-157000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-137000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-123000</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-19000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-20000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-28000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-52000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E33" s="3">
         <v>403000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>375000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>418000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>189000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>554000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>488000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>485000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>389000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>564000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1169000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E35" s="3">
         <v>403000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>375000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>418000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>189000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>554000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>488000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>485000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>389000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>564000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1169000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,35 +1963,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2563000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2504000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2418000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1939000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2327000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1445000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>500000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>525000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,8 +2005,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,35 +2049,38 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4305000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4557000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4438000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4441000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4387000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4301000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3990000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4141000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2000,35 +2093,38 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1989000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1960000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2128000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2264000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2256000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2155000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2200000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2237000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2041,35 +2137,38 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E45" s="3">
         <v>389000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>484000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>596000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>634000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>417000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>588000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>505000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,35 +2181,38 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9373000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9410000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9468000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9240000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9604000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8318000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7278000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7408000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,8 +2225,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,35 +2269,38 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2445000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2500000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2355000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2357000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2327000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2314000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2080000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2161000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2205,35 +2313,38 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14101000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14189000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14246000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14352000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14418000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14333000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14365000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14520000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,35 +2445,38 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6289000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6355000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6313000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6362000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6288000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2574000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2344000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2375000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,35 +2533,38 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32208000</v>
+      </c>
+      <c r="E54" s="3">
         <v>32454000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32382000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32311000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32637000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27539000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26067000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26464000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2577,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,35 +2615,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2931000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2947000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2774000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2835000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2977000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2944000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2687000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2702000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2526,35 +2657,38 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1008000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1006000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>5000</v>
       </c>
       <c r="G58" s="3">
         <v>5000</v>
       </c>
       <c r="H58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I58" s="3">
         <v>15000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,35 +2701,38 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4920000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5028000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4784000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4741000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5254000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4232000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3936000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3985000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2608,35 +2745,38 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8859000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8981000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7565000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7581000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8236000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7191000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6635000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6693000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,35 +2789,38 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8247000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8436000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10253000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10233000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10234000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8234000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2690,35 +2833,38 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7502000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7727000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7261000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7174000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7270000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2522000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2325000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2467000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,35 +3009,38 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24799000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25321000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25251000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25209000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25947000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18182000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9208000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9433000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,8 +3053,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,35 +3247,38 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1687000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1326000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>937000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>576000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>185000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11235000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18801000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18680000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3117,8 +3291,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,35 +3423,38 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7409000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7133000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7131000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7102000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6690000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9357000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16859000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17031000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3281,8 +3467,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E81" s="3">
         <v>403000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>375000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>418000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>189000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>554000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>488000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>485000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>389000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>564000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1169000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E83" s="3">
         <v>144000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>153000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>156000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>157000</v>
       </c>
       <c r="H83" s="3">
         <v>157000</v>
       </c>
       <c r="I83" s="3">
+        <v>157000</v>
+      </c>
+      <c r="J83" s="3">
         <v>160000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>157000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>159000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>154000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>316000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1050000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>650000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-67000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>468000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1042000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>622000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>468000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1040000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-94000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-80000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-70000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-143000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-74000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-73000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-88000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-120000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-84000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-266000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-95000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-118000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-85000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-145000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,20 +4144,21 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-13000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-14000</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,127 +4318,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-900000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-24000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-227000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>673000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-37000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-505000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>140000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-420000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1401000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E101" s="3">
         <v>24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-31000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-11000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>37000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-25000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-11000</v>
       </c>
       <c r="M101" s="3">
         <v>-11000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>-11000</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E102" s="3">
         <v>86000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>475000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-389000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>883000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>947000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>24000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-55000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-153000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-195000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>GEHC</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4839000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4650000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5206000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4822000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4817000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4707000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4938000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4576000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4484000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4343000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4589000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8692000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2837000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2749000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3050000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2887000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2877000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2816000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3006000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2803000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2688000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2665000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2727000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5146000</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2002000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1901000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2156000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1935000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1940000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1891000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1932000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1773000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1796000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1678000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1862000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3546000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E12" s="3">
         <v>324000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>315000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>322000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>298000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>270000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>271000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>260000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>257000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>238000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>225000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>391000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +983,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4231000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4110000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4517000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4205000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4247000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4148000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4161000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3971000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3853000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3834000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3862000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7276000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>608000</v>
+      </c>
+      <c r="E18" s="3">
         <v>540000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>689000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>617000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>570000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>559000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>777000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>605000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>631000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>509000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>727000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1416000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,228 +1208,244 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E20" s="3">
         <v>94000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>51000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>157000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>137000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>123000</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>19000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>20000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>28000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>52000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>858000</v>
+      </c>
+      <c r="E21" s="3">
         <v>782000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>884000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>927000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>863000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>839000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>934000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>784000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>808000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>696000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>915000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1784000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E22" s="3">
         <v>122000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>131000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>138000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>137000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>136000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>59000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E23" s="3">
         <v>512000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>609000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>636000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>570000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>546000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>718000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>622000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>639000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>533000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>755000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1444000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E24" s="3">
         <v>124000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>193000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>250000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>137000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>163000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>151000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>128000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>153000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>131000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>179000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>261000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E26" s="3">
         <v>388000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>416000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>386000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>433000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>383000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>567000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>494000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>486000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>402000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>576000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1183000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E27" s="3">
         <v>374000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>403000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>379000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>418000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>189000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>548000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>488000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>473000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>389000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>564000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1162000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,52 +1629,58 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-4000</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
         <v>6000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>12000</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>7000</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-94000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-51000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-157000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-137000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-123000</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-19000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-20000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-28000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-52000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E33" s="3">
         <v>374000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>403000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>375000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>418000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>189000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>554000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>488000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>485000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>389000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>564000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1169000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E35" s="3">
         <v>374000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>403000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>375000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>418000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>189000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>554000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>488000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>485000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>389000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>564000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1169000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,38 +2050,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2015000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2563000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2504000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2418000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1939000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2327000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1445000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>525000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2008,8 +2095,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,38 +2142,41 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4331000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4305000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4557000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4438000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4441000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4387000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4301000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3990000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4141000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,38 +2189,41 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2023000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1989000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1960000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2128000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2264000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2256000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2155000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2200000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2237000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2140,38 +2236,41 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E45" s="3">
         <v>516000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>389000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>484000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>596000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>634000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>417000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>588000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>505000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,38 +2283,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8806000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9373000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9410000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9468000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9240000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9604000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8318000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7278000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7408000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,8 +2330,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2272,38 +2377,41 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2458000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2445000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2500000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2355000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2357000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2327000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2314000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2080000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2161000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2316,38 +2424,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14311000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14101000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14189000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14246000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14352000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14418000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14333000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14365000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14520000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,38 +2565,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6277000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6289000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6355000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6313000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6362000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6288000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2574000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2344000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2375000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,38 +2659,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31852000</v>
+      </c>
+      <c r="E54" s="3">
         <v>32208000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32454000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32382000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32311000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32637000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27539000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26067000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26464000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2706,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,38 +2746,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2824000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2931000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2947000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2774000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2835000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2977000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2944000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2687000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2702000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2660,38 +2791,41 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1007000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1008000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1006000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5000</v>
       </c>
       <c r="H58" s="3">
         <v>5000</v>
       </c>
       <c r="I58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J58" s="3">
         <v>15000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,38 +2838,41 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4487000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4920000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5028000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4784000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4741000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5254000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4232000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3936000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3985000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,38 +2885,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8318000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8859000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8981000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7565000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7581000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8236000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7191000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6635000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6693000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,38 +2932,41 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8233000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8247000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8436000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10253000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10233000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10234000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8234000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2836,38 +2979,41 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7307000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7502000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7727000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7261000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7174000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7270000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2522000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2325000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2467000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,38 +3167,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24051000</v>
+      </c>
+      <c r="E66" s="3">
         <v>24799000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25321000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25251000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25209000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25947000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18182000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9208000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9433000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3214,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,38 +3421,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2101000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1687000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1326000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>937000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>576000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>185000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11235000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18801000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18680000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3294,8 +3468,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,38 +3609,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7801000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7409000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7133000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7131000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7102000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6690000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9357000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16859000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17031000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3656,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E81" s="3">
         <v>374000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>403000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>375000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>418000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>189000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>554000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>488000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>485000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>389000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>564000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1169000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +3823,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E83" s="3">
         <v>148000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>144000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>153000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>156000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>157000</v>
       </c>
       <c r="I83" s="3">
         <v>157000</v>
       </c>
       <c r="J83" s="3">
+        <v>157000</v>
+      </c>
+      <c r="K83" s="3">
         <v>160000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>157000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>159000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>154000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>316000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E89" s="3">
         <v>419000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1050000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>650000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-67000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>468000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1042000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>622000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>468000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1040000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4171,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-145000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-94000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-80000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-70000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-143000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-77000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-74000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-73000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-349000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-188000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-88000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-120000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-84000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-266000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-95000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-118000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-85000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-145000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4154,14 +4388,14 @@
         <v>-14000</v>
       </c>
       <c r="E96" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-13000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-14000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4564,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-153000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-900000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-24000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-227000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>673000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-37000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-505000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>140000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-420000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1401000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-19000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>24000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-31000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-11000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>37000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-25000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-11000</v>
       </c>
       <c r="N101" s="3">
         <v>-11000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>-11000</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-547000</v>
+      </c>
+      <c r="E102" s="3">
         <v>59000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>86000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>475000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-389000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>883000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>947000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>24000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-55000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-153000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-195000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>GEHC</t>
   </si>
@@ -656,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4863000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4839000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4650000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5206000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4822000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4817000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4707000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4938000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4576000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4484000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4343000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4589000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8692000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2838000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2837000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2749000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3050000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2887000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2877000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2816000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3006000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2803000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2688000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2665000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2727000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5146000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2025000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2002000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1901000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2156000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1935000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1940000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1891000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1932000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1773000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1796000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1678000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1862000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3546000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E12" s="3">
         <v>327000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>324000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>315000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>322000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>298000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>270000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>271000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>260000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>257000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>238000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>225000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>391000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,31 +1003,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-17000</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1033,31 +1053,34 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>143000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>148000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>144000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>156000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4231000</v>
+        <v>4082000</v>
       </c>
       <c r="E17" s="3">
-        <v>4110000</v>
+        <v>4126000</v>
       </c>
       <c r="F17" s="3">
-        <v>4517000</v>
+        <v>4006000</v>
       </c>
       <c r="G17" s="3">
-        <v>4205000</v>
+        <v>4359000</v>
       </c>
       <c r="H17" s="3">
-        <v>4247000</v>
+        <v>4087000</v>
       </c>
       <c r="I17" s="3">
-        <v>4148000</v>
+        <v>4125000</v>
       </c>
       <c r="J17" s="3">
+        <v>4031000</v>
+      </c>
+      <c r="K17" s="3">
         <v>4161000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3971000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3853000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3834000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3862000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7276000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>608000</v>
+        <v>781000</v>
       </c>
       <c r="E18" s="3">
-        <v>540000</v>
+        <v>713000</v>
       </c>
       <c r="F18" s="3">
-        <v>689000</v>
+        <v>644000</v>
       </c>
       <c r="G18" s="3">
-        <v>617000</v>
+        <v>847000</v>
       </c>
       <c r="H18" s="3">
-        <v>570000</v>
+        <v>735000</v>
       </c>
       <c r="I18" s="3">
-        <v>559000</v>
+        <v>692000</v>
       </c>
       <c r="J18" s="3">
+        <v>676000</v>
+      </c>
+      <c r="K18" s="3">
         <v>777000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>605000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>631000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>509000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>727000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1416000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,243 +1242,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>101000</v>
+        <v>-12000</v>
       </c>
       <c r="E20" s="3">
-        <v>94000</v>
+        <v>-6000</v>
       </c>
       <c r="F20" s="3">
-        <v>51000</v>
+        <v>-16000</v>
       </c>
       <c r="G20" s="3">
-        <v>157000</v>
+        <v>131000</v>
       </c>
       <c r="H20" s="3">
-        <v>137000</v>
+        <v>-25000</v>
       </c>
       <c r="I20" s="3">
-        <v>123000</v>
+        <v>-23000</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>19000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>20000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>28000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>52000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>858000</v>
+        <v>936000</v>
       </c>
       <c r="E21" s="3">
-        <v>782000</v>
+        <v>868000</v>
       </c>
       <c r="F21" s="3">
-        <v>884000</v>
+        <v>808000</v>
       </c>
       <c r="G21" s="3">
-        <v>927000</v>
+        <v>860000</v>
       </c>
       <c r="H21" s="3">
-        <v>863000</v>
+        <v>913000</v>
       </c>
       <c r="I21" s="3">
-        <v>839000</v>
+        <v>871000</v>
       </c>
       <c r="J21" s="3">
+        <v>835000</v>
+      </c>
+      <c r="K21" s="3">
         <v>934000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>784000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>808000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>696000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>915000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1784000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>148000</v>
+      </c>
+      <c r="G22" s="3">
         <v>131000</v>
       </c>
-      <c r="E22" s="3">
-        <v>122000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>131000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>138000</v>
-      </c>
       <c r="H22" s="3">
-        <v>137000</v>
+        <v>147000</v>
       </c>
       <c r="I22" s="3">
-        <v>136000</v>
+        <v>145000</v>
       </c>
       <c r="J22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="K22" s="3">
         <v>59000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>657000</v>
+      </c>
+      <c r="E23" s="3">
         <v>578000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>512000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>609000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>636000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>570000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>546000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>718000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>622000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>639000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>533000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>755000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1444000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E24" s="3">
         <v>143000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>124000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>193000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>250000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>137000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>163000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>151000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>128000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>153000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>131000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>179000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>261000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E26" s="3">
         <v>435000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>388000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>416000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>386000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>433000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>383000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>567000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>494000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>486000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>402000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>576000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1183000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E27" s="3">
         <v>428000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>374000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>403000</v>
       </c>
-      <c r="G27" s="3">
-        <v>379000</v>
-      </c>
       <c r="H27" s="3">
+        <v>375000</v>
+      </c>
+      <c r="I27" s="3">
         <v>418000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>189000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>548000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>488000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>473000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>389000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>564000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1162000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,55 +1690,61 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-4000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>6000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>12000</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>7000</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-101000</v>
+        <v>12000</v>
       </c>
       <c r="E32" s="3">
-        <v>-94000</v>
+        <v>6000</v>
       </c>
       <c r="F32" s="3">
-        <v>-51000</v>
+        <v>16000</v>
       </c>
       <c r="G32" s="3">
-        <v>-157000</v>
+        <v>-131000</v>
       </c>
       <c r="H32" s="3">
-        <v>-137000</v>
+        <v>25000</v>
       </c>
       <c r="I32" s="3">
-        <v>-123000</v>
+        <v>23000</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-19000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-20000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-28000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-52000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E33" s="3">
         <v>428000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>374000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>403000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>375000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>418000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>189000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>554000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>488000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>485000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>389000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>564000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1169000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E35" s="3">
         <v>428000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>374000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>403000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>375000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>418000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>189000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>554000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>488000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>485000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>389000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>564000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1169000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,41 +2137,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2015000</v>
+        <v>3550000</v>
       </c>
       <c r="E41" s="3">
-        <v>2563000</v>
+        <v>1998000</v>
       </c>
       <c r="F41" s="3">
-        <v>2504000</v>
+        <v>2551000</v>
       </c>
       <c r="G41" s="3">
-        <v>2418000</v>
+        <v>2494000</v>
       </c>
       <c r="H41" s="3">
-        <v>1939000</v>
+        <v>2408000</v>
       </c>
       <c r="I41" s="3">
-        <v>2327000</v>
+        <v>1936000</v>
       </c>
       <c r="J41" s="3">
+        <v>2324000</v>
+      </c>
+      <c r="K41" s="3">
         <v>1445000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>500000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>525000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2098,8 +2185,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,41 +2235,44 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4331000</v>
+        <v>4203000</v>
       </c>
       <c r="E43" s="3">
-        <v>4305000</v>
+        <v>4057000</v>
       </c>
       <c r="F43" s="3">
-        <v>4557000</v>
+        <v>4017000</v>
       </c>
       <c r="G43" s="3">
-        <v>4438000</v>
+        <v>4254000</v>
       </c>
       <c r="H43" s="3">
-        <v>4441000</v>
+        <v>4147000</v>
       </c>
       <c r="I43" s="3">
-        <v>4387000</v>
+        <v>4140000</v>
       </c>
       <c r="J43" s="3">
+        <v>4097000</v>
+      </c>
+      <c r="K43" s="3">
         <v>4301000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3990000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4141000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,41 +2285,44 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2124000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2023000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1989000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1960000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2128000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2264000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2256000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2155000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2200000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2237000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2239,41 +2335,44 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>437000</v>
+        <v>547000</v>
       </c>
       <c r="E45" s="3">
-        <v>516000</v>
+        <v>493000</v>
       </c>
       <c r="F45" s="3">
-        <v>389000</v>
+        <v>559000</v>
       </c>
       <c r="G45" s="3">
-        <v>484000</v>
+        <v>545000</v>
       </c>
       <c r="H45" s="3">
-        <v>596000</v>
+        <v>775000</v>
       </c>
       <c r="I45" s="3">
-        <v>634000</v>
+        <v>897000</v>
       </c>
       <c r="J45" s="3">
+        <v>924000</v>
+      </c>
+      <c r="K45" s="3">
         <v>417000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>588000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>505000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,41 +2385,44 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10638000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8806000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9373000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9410000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9468000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9240000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9604000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8318000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7278000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7408000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,31 +2435,34 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>361000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>357000</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2380,41 +2485,44 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2539000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2458000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2445000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2500000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2355000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2357000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2327000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2314000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2080000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2161000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2427,41 +2535,44 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14270000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14311000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14101000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14189000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14246000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14352000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14418000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14333000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14365000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14520000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,41 +2685,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6277000</v>
+        <v>1329000</v>
       </c>
       <c r="E52" s="3">
-        <v>6289000</v>
+        <v>1190000</v>
       </c>
       <c r="F52" s="3">
-        <v>6355000</v>
+        <v>1174000</v>
       </c>
       <c r="G52" s="3">
-        <v>6313000</v>
+        <v>1153000</v>
       </c>
       <c r="H52" s="3">
-        <v>6362000</v>
+        <v>1662000</v>
       </c>
       <c r="I52" s="3">
-        <v>6288000</v>
+        <v>1643000</v>
       </c>
       <c r="J52" s="3">
+        <v>1596000</v>
+      </c>
+      <c r="K52" s="3">
         <v>2574000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2344000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2375000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,41 +2785,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33855000</v>
+      </c>
+      <c r="E54" s="3">
         <v>31852000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32208000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32454000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32382000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32311000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32637000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27539000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26067000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26464000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +2835,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,41 +2877,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2911000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2824000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2931000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2947000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2774000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2835000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2977000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2944000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2687000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2702000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,41 +2925,44 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1007000</v>
+        <v>1121000</v>
       </c>
       <c r="E58" s="3">
-        <v>1008000</v>
+        <v>1120000</v>
       </c>
       <c r="F58" s="3">
-        <v>1006000</v>
+        <v>1117000</v>
       </c>
       <c r="G58" s="3">
+        <v>1116000</v>
+      </c>
+      <c r="H58" s="3">
         <v>7000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5000</v>
       </c>
       <c r="I58" s="3">
         <v>5000</v>
       </c>
       <c r="J58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2841,41 +2975,44 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4487000</v>
+        <v>2691000</v>
       </c>
       <c r="E59" s="3">
-        <v>4920000</v>
+        <v>2707000</v>
       </c>
       <c r="F59" s="3">
-        <v>5028000</v>
+        <v>2798000</v>
       </c>
       <c r="G59" s="3">
+        <v>2932000</v>
+      </c>
+      <c r="H59" s="3">
         <v>4784000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4741000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5254000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4232000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3936000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3985000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,41 +3025,44 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8670000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8318000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8859000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8981000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7565000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7581000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8236000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7191000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6635000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6693000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,41 +3075,44 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8233000</v>
+        <v>9612000</v>
       </c>
       <c r="E61" s="3">
-        <v>8247000</v>
+        <v>8542000</v>
       </c>
       <c r="F61" s="3">
-        <v>8436000</v>
+        <v>8551000</v>
       </c>
       <c r="G61" s="3">
-        <v>10253000</v>
+        <v>8747000</v>
       </c>
       <c r="H61" s="3">
-        <v>10233000</v>
+        <v>10618000</v>
       </c>
       <c r="I61" s="3">
-        <v>10234000</v>
+        <v>10603000</v>
       </c>
       <c r="J61" s="3">
+        <v>10575000</v>
+      </c>
+      <c r="K61" s="3">
         <v>8234000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2982,41 +3125,44 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7307000</v>
+        <v>910000</v>
       </c>
       <c r="E62" s="3">
-        <v>7502000</v>
+        <v>802000</v>
       </c>
       <c r="F62" s="3">
-        <v>7727000</v>
+        <v>818000</v>
       </c>
       <c r="G62" s="3">
-        <v>7261000</v>
+        <v>861000</v>
       </c>
       <c r="H62" s="3">
-        <v>7174000</v>
+        <v>778000</v>
       </c>
       <c r="I62" s="3">
-        <v>7270000</v>
+        <v>886000</v>
       </c>
       <c r="J62" s="3">
+        <v>843000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2522000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2325000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2467000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,41 +3325,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>24051000</v>
+        <v>25343000</v>
       </c>
       <c r="E66" s="3">
-        <v>24799000</v>
+        <v>23858000</v>
       </c>
       <c r="F66" s="3">
-        <v>25321000</v>
+        <v>24609000</v>
       </c>
       <c r="G66" s="3">
-        <v>25251000</v>
+        <v>25144000</v>
       </c>
       <c r="H66" s="3">
-        <v>25209000</v>
+        <v>25079000</v>
       </c>
       <c r="I66" s="3">
-        <v>25947000</v>
+        <v>24988000</v>
       </c>
       <c r="J66" s="3">
+        <v>25740000</v>
+      </c>
+      <c r="K66" s="3">
         <v>18182000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9208000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9433000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3375,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,41 +3595,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2558000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2101000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1687000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1326000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>937000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>576000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>185000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11235000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18801000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18680000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3645,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,41 +3795,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8317000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7801000</v>
       </c>
-      <c r="E76" s="3">
-        <v>7409000</v>
-      </c>
       <c r="F76" s="3">
+        <v>7408000</v>
+      </c>
+      <c r="G76" s="3">
         <v>7133000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7131000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7102000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6690000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9357000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16859000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17031000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +3845,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E81" s="3">
         <v>428000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>374000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>403000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>375000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>418000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>189000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>554000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>488000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>485000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>389000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>564000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1169000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>149000</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E83" s="3">
-        <v>148000</v>
+        <v>63000</v>
       </c>
       <c r="F83" s="3">
-        <v>144000</v>
+        <v>61000</v>
       </c>
       <c r="G83" s="3">
-        <v>153000</v>
+        <v>59000</v>
       </c>
       <c r="H83" s="3">
-        <v>156000</v>
-      </c>
-      <c r="I83" s="3">
+        <v>57000</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
+        <v>56000</v>
+      </c>
+      <c r="K83" s="3">
         <v>157000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
+        <v>160000</v>
+      </c>
+      <c r="M83" s="3">
         <v>157000</v>
       </c>
-      <c r="K83" s="3">
-        <v>160000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>157000</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>159000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>154000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>316000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-119000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>419000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1050000</v>
       </c>
-      <c r="G89" s="3">
-        <v>650000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>-67000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>468000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1042000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>622000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>468000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1040000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-64000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-145000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-94000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-80000</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-70000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-143000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-77000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-74000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-73000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-349000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-188000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-88000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-120000</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>-84000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-266000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-95000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-118000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-85000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-145000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,31 +4612,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-14000</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E96" s="3">
-        <v>-14000</v>
+        <v>14000</v>
       </c>
       <c r="F96" s="3">
-        <v>-13000</v>
+        <v>14000</v>
       </c>
       <c r="G96" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+        <v>13000</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>14000</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,145 +4810,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>-57000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-153000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-900000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-227000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>673000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-37000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-505000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>140000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-420000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1401000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-22000</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3">
-        <v>-19000</v>
+        <v>-11000</v>
       </c>
       <c r="F101" s="3">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="G101" s="3">
-        <v>-31000</v>
+        <v>37000</v>
       </c>
       <c r="H101" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>8000</v>
+        <v>-25000</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K101" s="3">
         <v>37000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-25000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-11000</v>
       </c>
       <c r="O101" s="3">
         <v>-11000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>-11000</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-547000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>59000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>86000</v>
       </c>
-      <c r="G102" s="3">
-        <v>475000</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-389000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>883000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>947000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>24000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-55000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-153000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-195000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
   <si>
     <t>GEHC</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5319000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4863000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4839000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4650000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5206000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4822000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4817000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4707000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4938000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4576000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4484000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4343000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4589000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8692000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3044000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2838000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2837000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2749000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3050000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2887000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2877000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2816000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3006000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2803000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2688000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2665000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2727000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5146000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2275000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2025000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2002000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1901000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2156000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1935000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1940000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1891000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1932000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1773000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1796000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1678000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1862000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3546000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,58 +918,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E12" s="3">
         <v>316000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>327000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>324000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>315000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>322000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>298000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>270000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>271000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>260000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>257000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>238000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>225000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>391000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,13 +1022,16 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-18000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1020,20 +1039,20 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-17000</v>
       </c>
-      <c r="H14" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1056,35 +1075,38 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E15" s="3">
         <v>143000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>149000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>148000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>144000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>153000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>156000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>157000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1106,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4433000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4082000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4126000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4006000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4359000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4498000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4087000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4125000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4031000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4161000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3971000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3853000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3834000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3862000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7276000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>886000</v>
+      </c>
+      <c r="E18" s="3">
         <v>781000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>713000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>644000</v>
       </c>
-      <c r="G18" s="3">
-        <v>847000</v>
-      </c>
       <c r="H18" s="3">
+        <v>708000</v>
+      </c>
+      <c r="I18" s="3">
         <v>735000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>692000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>676000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>777000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>605000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>631000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>509000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>727000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1416000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,258 +1275,274 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16000</v>
       </c>
-      <c r="G20" s="3">
-        <v>131000</v>
-      </c>
       <c r="H20" s="3">
+        <v>38000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>19000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>20000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>28000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>34000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>52000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>993000</v>
+      </c>
+      <c r="E21" s="3">
         <v>936000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>868000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>808000</v>
       </c>
-      <c r="G21" s="3">
-        <v>860000</v>
-      </c>
       <c r="H21" s="3">
+        <v>814000</v>
+      </c>
+      <c r="I21" s="3">
         <v>913000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>871000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>835000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>934000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>784000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>808000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>696000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>915000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1784000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>141000</v>
+        <v>37000</v>
       </c>
       <c r="E22" s="3">
         <v>141000</v>
       </c>
       <c r="F22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="G22" s="3">
         <v>148000</v>
       </c>
-      <c r="G22" s="3">
-        <v>131000</v>
-      </c>
       <c r="H22" s="3">
+        <v>68000</v>
+      </c>
+      <c r="I22" s="3">
         <v>147000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>145000</v>
       </c>
       <c r="J22" s="3">
         <v>145000</v>
       </c>
       <c r="K22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="L22" s="3">
         <v>59000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>834000</v>
+      </c>
+      <c r="E23" s="3">
         <v>657000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>578000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>512000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>609000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>636000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>570000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>546000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>718000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>622000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>639000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>533000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>755000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1444000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E24" s="3">
         <v>168000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>143000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>193000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>250000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>137000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>163000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>151000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>128000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>153000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>131000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>179000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>261000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>738000</v>
+      </c>
+      <c r="E26" s="3">
         <v>489000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>435000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>388000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>416000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>386000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>433000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>383000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>567000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>494000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>486000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>402000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>576000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1183000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E27" s="3">
         <v>470000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>428000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>374000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>403000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>375000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>418000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>189000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>548000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>488000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>473000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>389000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>564000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1162000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1711,40 +1771,43 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-4000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>6000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>12000</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>7000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E32" s="3">
         <v>12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-131000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-19000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-20000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-28000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-34000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E33" s="3">
         <v>470000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>428000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>374000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>403000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>375000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>418000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>189000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>554000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>488000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>485000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>389000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>564000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1169000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E35" s="3">
         <v>470000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>428000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>374000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>403000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>375000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>418000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>189000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>554000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>488000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>485000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>389000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>564000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1169000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,44 +2223,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2873000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3550000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1998000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2551000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2494000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2408000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1936000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2324000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1445000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>500000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>525000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,8 +2274,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,44 +2327,47 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4363000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4203000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4057000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4017000</v>
       </c>
-      <c r="G43" s="3">
-        <v>4254000</v>
-      </c>
       <c r="H43" s="3">
+        <v>4307000</v>
+      </c>
+      <c r="I43" s="3">
         <v>4147000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4140000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4097000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4301000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3990000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4141000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2288,44 +2380,47 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1939000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2124000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2023000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1989000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1960000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2128000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2264000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2256000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2155000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2200000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2237000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2338,44 +2433,47 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>522000</v>
+      </c>
+      <c r="E45" s="3">
         <v>547000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>493000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>559000</v>
       </c>
-      <c r="G45" s="3">
-        <v>545000</v>
-      </c>
       <c r="H45" s="3">
+        <v>492000</v>
+      </c>
+      <c r="I45" s="3">
         <v>775000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>897000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>924000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>417000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>588000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>505000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2388,44 +2486,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9901000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10638000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8806000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9373000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9410000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9468000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9240000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9604000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8318000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7278000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7408000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2438,34 +2539,37 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E47" s="3">
         <v>361000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>340000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>346000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>357000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2488,44 +2592,47 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2550000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2539000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2458000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2445000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2500000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2355000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2357000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2327000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2314000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2080000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2161000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,44 +2645,47 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14214000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14270000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14311000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14101000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14189000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14246000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14352000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14418000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14333000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14365000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14520000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,44 +2804,47 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1329000</v>
+        <v>1186000</v>
       </c>
       <c r="E52" s="3">
-        <v>1190000</v>
+        <v>1371000</v>
       </c>
       <c r="F52" s="3">
+        <v>1223000</v>
+      </c>
+      <c r="G52" s="3">
         <v>1174000</v>
       </c>
-      <c r="G52" s="3">
-        <v>1153000</v>
-      </c>
       <c r="H52" s="3">
+        <v>1178000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1662000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1643000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1596000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2574000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2344000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2375000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2738,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,44 +2910,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33089000</v>
+      </c>
+      <c r="E54" s="3">
         <v>33855000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31852000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32208000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32454000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32382000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32311000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32637000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27539000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26067000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26464000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,44 +3007,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3022000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2911000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2824000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2931000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2947000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2774000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2835000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2977000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2944000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2687000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2702000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,44 +3058,47 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1617000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1121000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1120000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1117000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1116000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>5000</v>
       </c>
       <c r="J58" s="3">
         <v>5000</v>
       </c>
       <c r="K58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,44 +3111,47 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2879000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2691000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2707000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2798000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2932000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4784000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4741000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5254000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4232000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3936000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3985000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,44 +3164,47 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9553000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8670000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8318000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8859000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8981000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7565000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7581000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8236000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7191000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6635000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6693000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3078,44 +3217,47 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7759000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9612000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8542000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8551000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8747000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10618000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10603000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10575000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8234000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3128,44 +3270,47 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>799000</v>
+      </c>
+      <c r="E62" s="3">
         <v>910000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>802000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>818000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>861000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>778000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>886000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>843000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2522000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2325000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2467000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3178,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,44 +3482,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24437000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25343000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23858000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24609000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25144000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25079000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24988000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25740000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18182000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9208000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9433000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3535,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,44 +3768,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3262000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2558000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2101000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1687000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1326000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>937000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>576000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>185000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11235000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18801000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18680000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,44 +3980,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8446000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8317000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7801000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7408000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7133000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7131000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7102000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6690000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9357000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16859000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17031000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3848,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E81" s="3">
         <v>470000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>428000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>374000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>403000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>375000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>418000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>189000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>554000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>488000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>485000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>389000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>564000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1169000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>60000</v>
       </c>
       <c r="E83" s="3">
+        <v>64000</v>
+      </c>
+      <c r="F83" s="3">
         <v>63000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>61000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>59000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>57000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>56000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>157000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>160000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>157000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>159000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>154000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>316000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>913000</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-119000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>419000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1050000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3">
+        <v>650000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-67000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>468000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1042000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>622000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>468000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1040000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-64000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-145000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-94000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-70000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-143000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-77000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-74000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-73000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>-240000</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-349000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-188000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-88000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3">
+        <v>-120000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-84000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-266000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-95000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-118000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-85000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-145000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,34 +4845,35 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
         <v>14000</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F96" s="3">
         <v>14000</v>
       </c>
       <c r="G96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="H96" s="3">
         <v>13000</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I96" s="3">
         <v>14000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="J96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,154 +5055,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>-1277000</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>-57000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-153000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-900000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-227000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>673000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-505000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>140000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-420000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1401000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>24000</v>
       </c>
       <c r="E101" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-11000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-25000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>37000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-25000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-12000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-11000</v>
       </c>
       <c r="P101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>-11000</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-679000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-547000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>59000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>86000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>475000</v>
+      </c>
+      <c r="J102" s="3">
         <v>-389000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>883000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>947000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>24000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-55000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-153000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-195000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4777000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5319000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4863000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4839000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4650000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5206000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4822000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4817000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4707000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4938000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4576000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4484000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4343000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4589000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8692000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2765000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3044000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2838000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2837000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2749000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3050000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2887000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2877000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2816000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3006000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2803000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2688000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2665000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2727000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5146000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2012000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2275000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2025000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2002000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1901000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2156000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1935000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1940000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1891000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1932000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1773000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1796000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1678000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1862000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3546000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -928,52 +942,55 @@
         <v>344000</v>
       </c>
       <c r="E12" s="3">
+        <v>344000</v>
+      </c>
+      <c r="F12" s="3">
         <v>316000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>327000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>324000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>315000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>322000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>298000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>270000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>271000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>260000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>257000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>238000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>225000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>391000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,37 +1042,40 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-18000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-17000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1078,38 +1098,41 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E15" s="3">
         <v>140000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>143000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>149000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>148000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>144000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>153000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>156000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>157000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4071000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4433000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4082000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4126000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4006000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4498000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4087000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4125000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4031000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4161000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3971000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3853000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3834000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3862000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7276000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>706000</v>
+      </c>
+      <c r="E18" s="3">
         <v>886000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>781000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>713000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>644000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>708000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>735000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>692000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>676000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>777000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>605000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>631000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>509000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>727000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1416000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,273 +1309,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E20" s="3">
         <v>33000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-16000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>38000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-25000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>19000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>20000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>28000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>34000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>52000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>854000</v>
+      </c>
+      <c r="E21" s="3">
         <v>993000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>936000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>868000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>808000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>814000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>913000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>871000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>835000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>934000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>784000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>808000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>696000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>915000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1784000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E22" s="3">
         <v>37000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>141000</v>
       </c>
       <c r="F22" s="3">
         <v>141000</v>
       </c>
       <c r="G22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="H22" s="3">
         <v>148000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>68000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>147000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>145000</v>
       </c>
       <c r="K22" s="3">
         <v>145000</v>
       </c>
       <c r="L22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="M22" s="3">
         <v>59000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24000</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>692000</v>
+      </c>
+      <c r="E23" s="3">
         <v>834000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>657000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>578000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>512000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>609000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>636000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>570000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>546000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>718000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>622000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>639000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>533000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>755000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1444000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E24" s="3">
         <v>96000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>168000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>143000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>124000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>193000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>250000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>137000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>163000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>151000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>128000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>153000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>131000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>179000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>261000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>588000</v>
+      </c>
+      <c r="E26" s="3">
         <v>738000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>489000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>435000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>388000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>416000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>386000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>433000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>383000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>567000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>494000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>486000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>402000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>576000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1183000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E27" s="3">
         <v>721000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>470000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>428000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>374000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>403000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>375000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>418000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>189000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>548000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>488000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>473000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>389000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>564000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1162000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1774,40 +1835,43 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-4000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>6000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>12000</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>7000</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-33000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>16000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-38000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>25000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-19000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-20000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-28000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-52000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E33" s="3">
         <v>721000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>470000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>428000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>374000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>403000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>375000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>418000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>189000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>554000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>488000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>485000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>389000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>564000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1169000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E35" s="3">
         <v>721000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>470000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>428000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>374000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>403000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>375000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>418000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>189000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>554000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>488000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>485000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>389000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>564000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1169000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,47 +2310,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2454000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2873000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3550000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1998000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2551000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2494000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2408000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1936000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2324000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1445000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>500000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>525000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2277,8 +2364,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,47 +2420,50 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4350000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4363000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4203000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4057000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4017000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4307000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4147000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4140000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4097000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4301000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3990000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4141000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2383,47 +2476,50 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2158000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1939000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2124000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2023000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1989000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1960000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2128000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2264000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2256000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2155000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2200000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2237000</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,47 +2532,50 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E45" s="3">
         <v>522000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>547000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>493000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>559000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>492000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>775000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>897000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>924000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>417000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>588000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>505000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,47 +2588,50 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9735000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9901000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10638000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8806000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9373000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9410000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9468000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9240000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9604000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8318000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7278000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7408000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,37 +2644,40 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E47" s="3">
         <v>373000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>361000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>340000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>346000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>357000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2595,47 +2700,50 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2851000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2550000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2539000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2458000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2445000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2500000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2355000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2357000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2327000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2314000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2080000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2161000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,47 +2756,50 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14611000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14214000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14270000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14311000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14101000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14189000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14246000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14352000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14418000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14333000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14365000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14520000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,47 +2924,50 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1180000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1186000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1371000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1223000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1174000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1178000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1662000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1643000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1596000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2574000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2344000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2375000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,47 +3036,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33586000</v>
+      </c>
+      <c r="E54" s="3">
         <v>33089000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33855000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31852000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32208000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32454000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32382000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32311000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32637000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27539000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26067000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26464000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,47 +3138,48 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3152000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3022000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2911000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2824000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2931000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2947000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2774000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2835000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2977000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2944000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2687000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2702000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,47 +3192,50 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2121000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1617000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1121000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1120000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1117000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1116000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>5000</v>
       </c>
       <c r="K58" s="3">
         <v>5000</v>
       </c>
       <c r="L58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M58" s="3">
         <v>15000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,47 +3248,50 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2879000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2691000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2707000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2798000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2932000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4784000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4741000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5254000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4232000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3936000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3985000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,47 +3304,50 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9969000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9553000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8670000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8318000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8859000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8981000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7565000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7581000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8236000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7191000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6635000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6693000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,47 +3360,50 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7063000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7759000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9612000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8542000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8551000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8747000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10618000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10603000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10575000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8234000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3273,47 +3416,50 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>810000</v>
+      </c>
+      <c r="E62" s="3">
         <v>799000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>910000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>802000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>818000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>861000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>778000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>886000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>843000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2522000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2325000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2467000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,47 +3640,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24168000</v>
+      </c>
+      <c r="E66" s="3">
         <v>24437000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25343000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23858000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24609000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25144000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25079000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24988000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25740000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18182000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9208000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9433000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3538,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,47 +3942,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3810000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3262000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2558000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2101000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1687000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1326000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>937000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>576000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>185000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11235000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18801000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18680000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3824,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,47 +4166,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9187000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8446000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8317000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7801000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7408000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7133000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7131000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7102000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6690000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9357000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16859000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17031000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4036,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E81" s="3">
         <v>721000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>470000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>428000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>374000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>403000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>375000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>418000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>189000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>554000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>488000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>485000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>389000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>564000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1169000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E83" s="3">
         <v>60000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>64000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>61000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>59000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>57000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>56000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>157000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>160000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>157000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>159000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>154000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>316000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E89" s="3">
         <v>913000</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3">
         <v>-119000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>419000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1050000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>650000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-67000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>468000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1042000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>622000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>468000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1040000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-152000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-102000</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3">
         <v>-64000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-145000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-94000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-80000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-70000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-143000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-77000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-74000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-59000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-407000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-240000</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3">
         <v>-349000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-188000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-88000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-120000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-84000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-266000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-95000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-118000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-85000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-145000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,37 +5079,38 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E96" s="3">
         <v>14000</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F96" s="3">
-        <v>14000</v>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G96" s="3">
         <v>14000</v>
       </c>
       <c r="H96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I96" s="3">
         <v>13000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>14000</v>
       </c>
       <c r="J96" s="3">
         <v>14000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,163 +5301,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-286000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1277000</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
         <v>-57000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-153000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-900000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-227000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>673000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-37000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-505000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>140000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-420000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1401000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E101" s="3">
         <v>24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-31000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-11000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>37000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-25000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>37000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-25000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-11000</v>
       </c>
       <c r="Q101" s="3">
         <v>-11000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>-11000</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-416000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-679000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-547000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>59000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>86000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>475000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-389000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>883000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>947000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>24000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-55000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-153000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-195000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5007000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4777000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5319000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4863000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4839000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4650000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5206000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4822000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4817000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4707000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4938000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4576000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4484000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4343000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4589000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8692000</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3023000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2765000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3044000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2838000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2837000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2749000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3050000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2887000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2877000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2816000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3006000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2803000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2688000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2665000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2727000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5146000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1984000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2012000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2275000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2025000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2002000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1901000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2156000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1935000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1940000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1891000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1932000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1773000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1796000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1678000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1862000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3546000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>344000</v>
+        <v>302000</v>
       </c>
       <c r="E12" s="3">
         <v>344000</v>
       </c>
       <c r="F12" s="3">
+        <v>344000</v>
+      </c>
+      <c r="G12" s="3">
         <v>316000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>327000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>324000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>315000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>322000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>298000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>270000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>271000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>260000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>257000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>238000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>225000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>391000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,40 +1062,43 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-96000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-18000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-17000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1101,41 +1121,44 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E15" s="3">
         <v>136000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>140000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>143000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>149000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>148000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>144000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>153000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>156000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>157000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4275000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4071000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4433000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4082000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4126000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4006000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4498000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4087000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4125000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4031000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4161000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3971000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3853000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3834000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3862000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7276000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>732000</v>
+      </c>
+      <c r="E18" s="3">
         <v>706000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>886000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>781000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>713000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>644000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>708000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>735000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>692000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>676000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>777000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>605000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>631000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>509000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>727000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1416000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,288 +1343,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>33000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-12000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-16000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>38000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-25000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-23000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>19000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>20000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>28000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>34000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>52000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E21" s="3">
         <v>854000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>993000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>936000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>868000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>808000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>814000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>913000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>871000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>835000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>934000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>784000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>808000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>696000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>915000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1784000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E22" s="3">
         <v>122000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>141000</v>
       </c>
       <c r="G22" s="3">
         <v>141000</v>
       </c>
       <c r="H22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="I22" s="3">
         <v>148000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>68000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>147000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>145000</v>
       </c>
       <c r="L22" s="3">
         <v>145000</v>
       </c>
       <c r="M22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="N22" s="3">
         <v>59000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24000</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>613000</v>
+      </c>
+      <c r="E23" s="3">
         <v>692000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>834000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>657000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>578000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>512000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>609000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>636000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>570000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>546000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>718000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>622000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>639000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>533000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>755000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1444000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E24" s="3">
         <v>104000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>96000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>168000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>143000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>124000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>193000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>250000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>137000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>163000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>151000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>128000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>153000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>131000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>179000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>261000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E26" s="3">
         <v>588000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>738000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>489000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>435000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>388000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>416000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>386000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>433000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>383000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>567000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>494000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>486000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>402000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>576000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1183000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E27" s="3">
         <v>564000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>721000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>470000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>428000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>374000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>403000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>375000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>418000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>189000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>548000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>488000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>473000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>389000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>564000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1162000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1838,40 +1899,43 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-4000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>6000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>12000</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>7000</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-33000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>12000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>16000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-38000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>25000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>23000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-19000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-20000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-34000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-52000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E33" s="3">
         <v>564000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>721000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>470000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>428000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>374000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>403000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>375000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>418000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>189000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>554000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>488000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>485000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>389000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>564000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1169000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E35" s="3">
         <v>564000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>721000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>470000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>428000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>374000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>403000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>375000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>418000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>189000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>554000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>488000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>485000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>389000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>564000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1169000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,50 +2397,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3737000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2454000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2873000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3550000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1998000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2551000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2494000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2408000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1936000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2324000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1445000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>525000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,50 +2513,53 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4475000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4350000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4363000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4203000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4057000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4017000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4307000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4147000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4140000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4097000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4301000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3990000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4141000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2479,50 +2572,53 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2283000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2158000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1939000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2124000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2023000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1989000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1960000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2128000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2264000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2256000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2155000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2200000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2237000</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,50 +2631,53 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E45" s="3">
         <v>505000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>522000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>547000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>493000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>559000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>492000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>775000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>897000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>924000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>417000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>588000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>505000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,50 +2690,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11308000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9735000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9901000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10638000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8806000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9373000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9410000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9468000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9240000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9604000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8318000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7278000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7408000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,40 +2749,43 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E47" s="3">
         <v>235000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>373000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>361000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>340000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>346000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>357000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2703,50 +2808,53 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2962000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2851000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2550000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2539000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2458000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2445000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2500000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2355000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2357000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2327000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2314000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2080000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2161000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2759,50 +2867,53 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14637000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14611000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14214000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14270000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14311000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14101000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14189000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14246000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14352000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14418000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14333000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14365000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14520000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,50 +3044,53 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1292000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1180000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1186000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1371000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1223000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1174000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1178000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1662000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1643000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1596000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2574000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2344000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2375000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,50 +3162,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>35500000</v>
+      </c>
+      <c r="E54" s="3">
         <v>33586000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33089000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33855000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31852000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32208000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32454000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32382000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32311000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32637000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27539000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26067000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26464000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,50 +3269,51 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3152000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3022000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2911000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2824000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2931000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2947000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2774000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2835000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2977000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2944000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2687000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2702000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,50 +3326,53 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2132000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2121000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1617000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1121000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1120000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1117000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1116000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>5000</v>
       </c>
       <c r="L58" s="3">
         <v>5000</v>
       </c>
       <c r="M58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N58" s="3">
         <v>15000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3251,50 +3385,53 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2767000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2820000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2879000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2691000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2707000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2798000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2932000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4784000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4741000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5254000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4232000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3936000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3985000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,50 +3444,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9748000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9969000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9553000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8670000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8318000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8859000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8981000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7565000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7581000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8236000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7191000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6635000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6693000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,50 +3503,53 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8584000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7063000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7759000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9612000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8542000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8551000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8747000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10618000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10603000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10575000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8234000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3419,50 +3562,53 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>950000</v>
+      </c>
+      <c r="E62" s="3">
         <v>810000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>799000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>910000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>802000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>818000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>861000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>778000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>886000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>843000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2522000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2325000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2467000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,50 +3798,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25547000</v>
+      </c>
+      <c r="E66" s="3">
         <v>24168000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24437000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25343000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23858000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24609000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25144000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25079000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24988000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25740000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18182000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9208000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9433000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,50 +4116,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4295000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3810000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3262000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2558000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2101000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1687000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1326000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>937000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>576000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>185000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11235000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18801000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18680000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,50 +4352,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9712000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9187000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8446000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8317000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7801000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7408000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7133000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7131000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7102000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6690000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9357000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16859000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17031000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E81" s="3">
         <v>564000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>721000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>470000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>428000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>374000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>403000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>375000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>418000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>189000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>554000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>488000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>485000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>389000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>564000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1169000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E83" s="3">
         <v>68000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>60000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>64000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>61000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>59000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>57000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>56000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>157000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>160000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>157000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>159000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>154000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>316000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E89" s="3">
         <v>250000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>913000</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>-119000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>419000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1050000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>650000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-67000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>468000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1042000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>622000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>468000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1040000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-152000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-102000</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-64000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-145000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-94000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-80000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-70000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-143000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-77000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-74000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-73000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-223000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-407000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-240000</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>-349000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-188000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-88000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-120000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-84000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-266000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-95000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-118000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-85000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-145000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5089,31 +5323,31 @@
         <v>16000</v>
       </c>
       <c r="E96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F96" s="3">
         <v>14000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G96" s="3">
-        <v>14000</v>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H96" s="3">
         <v>14000</v>
       </c>
       <c r="I96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J96" s="3">
         <v>13000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>14000</v>
       </c>
       <c r="K96" s="3">
         <v>14000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-286000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1277000</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>-57000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-153000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-900000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-24000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-227000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>673000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-37000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-505000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>140000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-420000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1401000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-19000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>24000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-31000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-11000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>37000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-25000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>37000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-25000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-11000</v>
       </c>
       <c r="R101" s="3">
         <v>-11000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>-11000</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1289000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-416000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-679000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-547000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>59000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>86000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>475000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-389000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>883000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>947000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-153000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-195000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5698000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5143000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5007000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4777000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5319000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4863000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4839000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4650000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5206000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4822000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4817000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4707000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4938000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4576000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4484000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4343000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4589000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8692000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3437000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3154000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3023000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2765000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3044000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2838000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2837000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2749000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3050000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2887000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2877000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2816000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3006000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2803000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2688000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2665000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2727000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5146000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2261000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1989000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1984000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2012000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2275000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2025000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2002000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1901000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2156000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1935000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1940000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1891000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1932000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1773000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1796000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1678000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1862000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3546000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E12" s="3">
         <v>292000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>302000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>344000</v>
       </c>
       <c r="G12" s="3">
         <v>344000</v>
       </c>
       <c r="H12" s="3">
+        <v>344000</v>
+      </c>
+      <c r="I12" s="3">
         <v>316000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>327000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>324000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>315000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>322000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>298000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>270000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>271000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>260000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>257000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>238000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>225000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>391000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,25 +1101,28 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-96000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>1000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1111,20 +1130,20 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-17000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1147,47 +1166,50 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>148000</v>
+        <v>146000</v>
       </c>
       <c r="E15" s="3">
         <v>148000</v>
       </c>
       <c r="F15" s="3">
+        <v>148000</v>
+      </c>
+      <c r="G15" s="3">
         <v>136000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>140000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>143000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>149000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>148000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>144000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>153000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>156000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>157000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4802000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4412000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4275000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4071000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4433000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4414000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4082000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4126000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4006000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4498000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4087000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4125000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4031000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4161000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3971000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3853000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3834000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3862000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7276000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>896000</v>
+      </c>
+      <c r="E18" s="3">
         <v>731000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>732000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>706000</v>
       </c>
-      <c r="G18" s="3">
-        <v>886000</v>
-      </c>
       <c r="H18" s="3">
+        <v>905000</v>
+      </c>
+      <c r="I18" s="3">
         <v>781000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>713000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>644000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>708000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>735000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>692000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>676000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>777000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>605000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>631000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>509000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>727000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1416000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,318 +1410,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-28000</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-12000</v>
       </c>
-      <c r="G20" s="3">
-        <v>33000</v>
-      </c>
       <c r="H20" s="3">
+        <v>495000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-16000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>38000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-23000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>19000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>20000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>28000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>34000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>52000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E21" s="3">
         <v>907000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>880000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>854000</v>
       </c>
-      <c r="G21" s="3">
-        <v>993000</v>
-      </c>
       <c r="H21" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I21" s="3">
         <v>936000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>868000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>808000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>814000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>913000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>871000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>835000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>934000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>784000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>808000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>696000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>915000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1784000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-375000</v>
+      </c>
+      <c r="E22" s="3">
         <v>128000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>124000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>122000</v>
       </c>
-      <c r="G22" s="3">
-        <v>37000</v>
-      </c>
       <c r="H22" s="3">
-        <v>141000</v>
+        <v>-425000</v>
       </c>
       <c r="I22" s="3">
         <v>141000</v>
       </c>
       <c r="J22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="K22" s="3">
         <v>148000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>68000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>147000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>145000</v>
       </c>
       <c r="N22" s="3">
         <v>145000</v>
       </c>
       <c r="O22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="P22" s="3">
         <v>59000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>24000</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>821000</v>
+      </c>
+      <c r="E23" s="3">
         <v>643000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>613000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>692000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>834000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>657000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>578000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>512000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>609000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>636000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>570000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>546000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>718000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>622000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>639000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>533000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>755000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1444000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E24" s="3">
         <v>179000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>113000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>104000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>96000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>168000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>143000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>124000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>193000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>250000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>137000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>163000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>151000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>128000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>153000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>131000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>179000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>261000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>602000</v>
+      </c>
+      <c r="E26" s="3">
         <v>464000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>500000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>588000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>738000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>489000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>435000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>388000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>416000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>386000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>433000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>383000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>567000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>494000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>486000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>402000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>576000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1183000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E27" s="3">
         <v>446000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>486000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>564000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>721000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>470000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>428000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>374000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>403000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>375000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>418000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>189000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>548000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>488000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>473000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>389000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>564000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1162000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1966,40 +2026,43 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-4000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>6000</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>12000</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>7000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-474000</v>
+      </c>
+      <c r="E32" s="3">
         <v>28000</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>12000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-33000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-495000</v>
+      </c>
+      <c r="I32" s="3">
         <v>12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>16000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-38000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>23000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-20000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-28000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-34000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-52000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E33" s="3">
         <v>446000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>486000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>564000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>721000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>470000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>428000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>374000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>403000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>375000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>418000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>189000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>554000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>488000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>485000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>389000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>564000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1169000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E35" s="3">
         <v>446000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>486000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>564000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>721000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>470000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>428000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>374000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>403000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>375000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>418000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>189000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>554000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>488000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>485000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>389000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>564000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1169000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,56 +2570,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4492000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4005000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3737000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2454000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2873000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3550000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1998000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2551000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2494000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2408000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1936000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2324000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1445000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>525000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,56 +2698,59 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4849000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4681000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4475000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4350000</v>
       </c>
-      <c r="G43" s="3">
-        <v>4363000</v>
-      </c>
       <c r="H43" s="3">
+        <v>4360000</v>
+      </c>
+      <c r="I43" s="3">
         <v>4203000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4057000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4017000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4307000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4147000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4140000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4097000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4301000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3990000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4141000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2671,56 +2763,59 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2234000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2304000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2283000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2158000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1939000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2124000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2023000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1989000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1960000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2128000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2264000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2256000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2155000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2200000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2237000</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,56 +2828,59 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>679000</v>
+      </c>
+      <c r="E45" s="3">
         <v>646000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>550000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>505000</v>
       </c>
-      <c r="G45" s="3">
-        <v>522000</v>
-      </c>
       <c r="H45" s="3">
+        <v>525000</v>
+      </c>
+      <c r="I45" s="3">
         <v>547000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>493000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>559000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>492000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>775000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>897000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>924000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>417000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>588000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>505000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,56 +2893,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12501000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11893000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11308000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9735000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9901000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10638000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8806000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9373000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9410000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9468000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9240000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9604000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8318000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7278000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7408000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,46 +2958,49 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E47" s="3">
         <v>302000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>244000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>235000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>373000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>361000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>340000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>346000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>357000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2919,56 +3023,59 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3092000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3010000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2962000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2851000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2550000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2539000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2458000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2445000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2500000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2355000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2357000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2327000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2314000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2080000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2161000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,56 +3088,59 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14619000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14604000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14637000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14611000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14214000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14270000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14311000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14101000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14189000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14246000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14352000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14418000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14333000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14365000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14520000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,56 +3283,59 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1251000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1281000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1292000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1180000</v>
       </c>
-      <c r="G52" s="3">
-        <v>1186000</v>
-      </c>
       <c r="H52" s="3">
+        <v>1102000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1371000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1223000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1174000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1178000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1662000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1643000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1596000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2574000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2344000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2375000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,56 +3413,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36906000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36127000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>35500000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33586000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33089000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33855000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31852000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32208000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32454000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32382000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32311000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32637000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27539000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26067000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26464000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,56 +3530,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3250000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2987000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2975000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3152000</v>
       </c>
-      <c r="G57" s="3">
-        <v>3022000</v>
-      </c>
       <c r="H57" s="3">
+        <v>3035000</v>
+      </c>
+      <c r="I57" s="3">
         <v>2911000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2824000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2931000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2947000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2774000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2835000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2977000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2944000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2687000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2702000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,56 +3593,59 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>642000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2139000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2132000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2121000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1617000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1121000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1120000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1117000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1116000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>5000</v>
       </c>
       <c r="N58" s="3">
         <v>5000</v>
       </c>
       <c r="O58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P58" s="3">
         <v>15000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,56 +3658,59 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2983000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2812000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2767000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2820000</v>
       </c>
-      <c r="G59" s="3">
-        <v>2879000</v>
-      </c>
       <c r="H59" s="3">
+        <v>2866000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2691000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2707000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2798000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2932000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4784000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4741000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5254000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4232000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3936000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3985000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,56 +3723,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9105000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10073000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9748000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9969000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9553000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8670000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8318000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8859000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8981000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7565000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7581000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8236000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7191000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6635000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6693000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,56 +3788,59 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9821000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8605000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8584000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7063000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7759000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9612000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8542000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8551000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8747000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10618000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10603000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10575000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8234000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30000</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3711,56 +3853,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>932000</v>
+      </c>
+      <c r="E62" s="3">
         <v>996000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>950000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>810000</v>
       </c>
-      <c r="G62" s="3">
-        <v>799000</v>
-      </c>
       <c r="H62" s="3">
+        <v>800000</v>
+      </c>
+      <c r="I62" s="3">
         <v>910000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>802000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>818000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>861000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>778000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>886000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>843000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2522000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2325000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2467000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,56 +4113,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26307000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25907000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25547000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24168000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24437000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25343000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23858000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24609000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25144000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25079000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24988000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25740000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18182000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9208000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9433000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,56 +4463,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5281000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4709000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4295000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3810000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3262000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2558000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2101000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1687000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1326000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>937000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>576000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>185000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11235000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18801000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18680000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,56 +4723,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10379000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9993000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9712000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9187000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8446000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8317000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7801000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7408000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7133000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7131000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7102000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6690000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9357000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16859000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17031000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E81" s="3">
         <v>446000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>486000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>564000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>721000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>470000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>428000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>374000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>403000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>375000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>418000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>189000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>554000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>488000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>485000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>389000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>564000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1169000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>69000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>68000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>60000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>64000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>63000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>61000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>59000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>57000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>56000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>157000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>160000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>157000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>159000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>154000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>316000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1050000</v>
+      </c>
+      <c r="E89" s="3">
         <v>593000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>94000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>250000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>913000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-119000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>419000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1050000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>650000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-67000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>468000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1042000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>622000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-19000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>468000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1040000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-110000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-86000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-152000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-102000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
         <v>-64000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-145000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-94000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-80000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-70000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-143000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-77000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-59000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-73000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-269000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-148000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-223000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-407000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-240000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-349000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-188000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-88000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-120000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-84000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-266000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-95000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-118000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-85000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-145000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5563,31 +5796,31 @@
         <v>16000</v>
       </c>
       <c r="G96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H96" s="3">
         <v>14000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3">
-        <v>14000</v>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J96" s="3">
         <v>14000</v>
       </c>
       <c r="K96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="L96" s="3">
         <v>13000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>14000</v>
       </c>
       <c r="M96" s="3">
         <v>14000</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-292000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-165000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1361000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-286000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1277000</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="H100" s="3">
+        <v>-1276000</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-57000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-153000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-900000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-24000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-227000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>673000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-37000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-505000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>140000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-420000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1401000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3">
         <v>-22000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-19000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>24000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-31000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-11000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>37000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-25000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>37000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-12000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-11000</v>
       </c>
       <c r="T101" s="3">
         <v>-11000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>-11000</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E102" s="3">
         <v>264000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1289000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-416000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-679000</v>
-      </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>-678000</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-547000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>59000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>86000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>475000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-389000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>883000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>947000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-55000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-153000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-195000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>GEHC</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5131000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5698000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5143000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5007000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4777000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5319000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4863000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4839000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4650000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5206000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4822000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4817000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4707000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4938000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4576000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4484000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4343000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4589000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8692000</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3154000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3437000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3154000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3023000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2765000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3044000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2838000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2837000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2749000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3050000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2887000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2877000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2816000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3006000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2803000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2688000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2665000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2727000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5146000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2261000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1989000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1984000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2012000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2275000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2025000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2002000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1901000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2156000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1935000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1940000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1891000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1932000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1773000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1796000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1678000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1862000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3546000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E12" s="3">
         <v>323000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>292000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>302000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>344000</v>
       </c>
       <c r="H12" s="3">
         <v>344000</v>
       </c>
       <c r="I12" s="3">
+        <v>344000</v>
+      </c>
+      <c r="J12" s="3">
         <v>316000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>327000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>324000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>315000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>322000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>298000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>270000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>271000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>260000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>257000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>238000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>225000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>391000</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,49 +1121,52 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-96000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-17000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1169,50 +1189,53 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E15" s="3">
         <v>146000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>148000</v>
       </c>
       <c r="F15" s="3">
         <v>148000</v>
       </c>
       <c r="G15" s="3">
+        <v>148000</v>
+      </c>
+      <c r="H15" s="3">
         <v>136000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>140000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>143000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>149000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>148000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>144000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>153000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>156000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>157000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4562000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4802000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4412000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4275000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4071000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4414000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4082000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4126000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4006000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4498000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4087000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4125000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4031000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4161000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3971000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3853000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3834000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3862000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7276000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>569000</v>
+      </c>
+      <c r="E18" s="3">
         <v>896000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>731000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>732000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>706000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>905000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>781000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>713000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>644000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>708000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>735000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>692000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>676000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>777000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>605000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>631000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>509000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>727000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1416000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,333 +1444,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>474000</v>
+        <v>-51000</v>
       </c>
       <c r="E20" s="3">
+        <v>93000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-28000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-12000</v>
       </c>
-      <c r="H20" s="3">
-        <v>495000</v>
-      </c>
       <c r="I20" s="3">
+        <v>33000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-16000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>38000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-25000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-23000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>19000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>20000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>28000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>34000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>52000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>568000</v>
+        <v>773000</v>
       </c>
       <c r="E21" s="3">
+        <v>949000</v>
+      </c>
+      <c r="F21" s="3">
         <v>907000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>880000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>854000</v>
       </c>
-      <c r="H21" s="3">
-        <v>550000</v>
-      </c>
       <c r="I21" s="3">
+        <v>1012000</v>
+      </c>
+      <c r="J21" s="3">
         <v>936000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>868000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>808000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>814000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>913000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>871000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>835000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>934000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>784000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>808000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>696000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>915000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1784000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>-375000</v>
+        <v>115000</v>
       </c>
       <c r="E22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F22" s="3">
         <v>128000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>124000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>122000</v>
       </c>
-      <c r="H22" s="3">
-        <v>-425000</v>
-      </c>
       <c r="I22" s="3">
-        <v>141000</v>
+        <v>37000</v>
       </c>
       <c r="J22" s="3">
         <v>141000</v>
       </c>
       <c r="K22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="L22" s="3">
         <v>148000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>68000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>147000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>145000</v>
       </c>
       <c r="O22" s="3">
         <v>145000</v>
       </c>
       <c r="P22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>59000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>24000</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E23" s="3">
         <v>821000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>643000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>613000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>692000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>834000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>657000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>578000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>512000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>609000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>636000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>570000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>546000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>718000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>622000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>639000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>533000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>755000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1444000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E24" s="3">
         <v>219000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>179000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>113000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>104000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>96000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>168000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>143000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>124000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>193000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>250000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>137000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>163000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>151000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>128000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>153000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>131000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>179000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>261000</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E26" s="3">
         <v>602000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>464000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>500000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>588000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>738000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>489000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>435000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>388000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>416000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>386000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>433000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>383000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>567000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>494000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>486000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>402000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>576000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1183000</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E27" s="3">
         <v>589000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>446000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>486000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>564000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>721000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>470000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>428000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>374000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>403000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>375000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>418000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>189000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>548000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>488000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>473000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>389000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>564000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1162000</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2029,40 +2090,43 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-4000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>6000</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>12000</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>7000</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-474000</v>
+        <v>51000</v>
       </c>
       <c r="E32" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F32" s="3">
         <v>28000</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>12000</v>
       </c>
-      <c r="H32" s="3">
-        <v>-495000</v>
-      </c>
       <c r="I32" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="J32" s="3">
         <v>12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>16000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-38000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>25000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>23000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-19000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-20000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-28000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-34000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-52000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E33" s="3">
         <v>589000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>446000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>486000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>564000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>721000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>470000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>428000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>374000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>403000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>375000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>418000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>189000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>554000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>488000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>485000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>389000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>564000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1169000</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E35" s="3">
         <v>589000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>446000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>486000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>564000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>721000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>470000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>428000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>374000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>403000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>375000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>418000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>189000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>554000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>488000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>485000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>389000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>564000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1169000</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,59 +2657,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2261000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4492000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4005000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3737000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2454000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2873000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3550000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1998000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2551000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2494000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2408000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1936000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2324000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1445000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>525000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,59 +2791,62 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4739000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4849000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4681000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4475000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4350000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4360000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4203000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4057000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4017000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4307000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4147000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4140000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4097000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4301000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3990000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4141000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2766,59 +2859,62 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2353000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2234000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2304000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2283000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2158000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1939000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2124000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2023000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1989000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1960000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2128000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2264000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2256000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2155000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2200000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2237000</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2831,59 +2927,62 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>729000</v>
+      </c>
+      <c r="E45" s="3">
         <v>679000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>646000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>550000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>505000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>525000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>547000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>493000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>559000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>492000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>775000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>897000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>924000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>417000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>588000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>505000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2896,59 +2995,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10426000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12501000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11893000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11308000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9735000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9901000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10638000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8806000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9373000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9410000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9468000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9240000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9604000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8318000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7278000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7408000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2961,49 +3063,52 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E47" s="3">
         <v>351000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>302000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>244000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>235000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>373000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>361000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>340000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>346000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>357000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3026,59 +3131,62 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3095000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3092000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3010000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2962000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2851000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2550000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2539000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2458000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2445000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2500000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2355000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2357000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2327000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2314000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2080000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2161000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,59 +3199,62 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16968000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14619000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14604000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14637000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14611000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14214000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14270000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14311000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14101000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14189000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14246000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14352000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14418000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14333000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14365000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14520000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,59 +3403,62 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1277000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1251000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1281000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1292000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1180000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1102000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1371000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1223000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1174000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1178000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1662000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1643000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1596000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2574000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2344000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2375000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,59 +3539,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37125000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36906000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36127000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35500000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33586000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33089000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33855000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31852000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32208000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32454000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32382000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32311000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32637000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27539000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26067000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26464000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,59 +3661,60 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3410000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3250000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2987000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2975000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3152000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3035000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2911000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2824000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2931000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2947000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2774000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2835000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2977000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2944000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2687000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2702000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,59 +3727,62 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E58" s="3">
         <v>642000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2139000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2132000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2121000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1617000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1121000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1120000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1117000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1116000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>5000</v>
       </c>
       <c r="O58" s="3">
         <v>5000</v>
       </c>
       <c r="P58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>15000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3661,59 +3795,62 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2998000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2983000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2812000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2767000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2820000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2866000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2691000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2707000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2798000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2932000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4784000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4741000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5254000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4232000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3936000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3985000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,59 +3863,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8529000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9105000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10073000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9748000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9969000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9553000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8670000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8318000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8859000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8981000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7565000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7581000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8236000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7191000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6635000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6693000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3791,59 +3931,62 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10438000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9821000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8605000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8584000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7063000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7759000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9612000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8542000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8551000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8747000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10618000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10603000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10575000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8234000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>30000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3856,59 +3999,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>885000</v>
+      </c>
+      <c r="E62" s="3">
         <v>932000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>996000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>950000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>810000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>910000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>802000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>818000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>861000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>778000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>886000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>843000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2522000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2325000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2467000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,59 +4271,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26227000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26307000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25907000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25547000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24168000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24437000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25343000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23858000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24609000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25144000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25079000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>24988000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25740000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18182000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9208000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9433000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,59 +4637,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5654000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5281000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4709000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4295000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3810000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3262000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2558000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2101000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1687000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1326000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>937000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>576000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>185000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11235000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18801000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18680000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,59 +4909,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10668000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10379000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9993000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9712000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9187000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8446000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8317000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7801000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7408000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7133000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7131000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7102000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6690000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9357000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16859000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17031000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E81" s="3">
         <v>589000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>446000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>486000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>564000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>721000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>470000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>428000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>374000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>403000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>375000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>418000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>189000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>554000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>488000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>485000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>389000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>564000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1169000</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E83" s="3">
         <v>65000</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
         <v>69000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>68000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>60000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>63000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>61000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>59000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>57000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>56000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>157000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>160000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>157000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>159000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>154000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>316000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1050000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>593000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>94000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>250000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>913000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-119000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>419000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1050000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>650000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-67000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>468000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1042000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>622000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>468000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1040000</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-134000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-110000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-86000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-152000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-102000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-64000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-145000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-94000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-80000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-70000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-143000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-74000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-59000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-73000</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-269000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-148000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-223000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-407000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-240000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-349000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-188000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-88000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-120000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-84000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-266000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-118000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-85000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-145000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5799,31 +6033,31 @@
         <v>16000</v>
       </c>
       <c r="H96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I96" s="3">
         <v>14000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3">
-        <v>14000</v>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>14000</v>
       </c>
       <c r="L96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M96" s="3">
         <v>13000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>14000</v>
       </c>
       <c r="N96" s="3">
         <v>14000</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-292000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-165000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1361000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-286000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1276000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-57000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-153000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-900000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-24000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-227000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>673000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-505000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>140000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-420000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1401000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-75000</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3">
         <v>-22000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-19000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>24000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-31000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>37000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-25000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>37000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-25000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-11000</v>
       </c>
       <c r="U101" s="3">
         <v>-11000</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="V101" s="3">
+        <v>-11000</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2226000</v>
+      </c>
+      <c r="E102" s="3">
         <v>487000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>264000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1289000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-416000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-678000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-547000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>59000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>86000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>475000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-389000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>883000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>947000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>24000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-55000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-153000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-195000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
